--- a/github_image_links.xlsx
+++ b/github_image_links.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPAberaman Park Industrial Estate___Aberdare_CF44 6DA_U0377.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPAberaman Park Industrial Estate___Aberdare_CF44 6DA_U0377.png</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPHarmire Enterprise Park_Harmire Road__Barnard Castle_DL12 8BN_U0325.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPHarmire Enterprise Park_Harmire Road__Barnard Castle_DL12 8BN_U0325.png</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPBakers Court_Paycocke Road__Basildon_SS14 3EH_U0198.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBakers Court_Paycocke Road__Basildon_SS14 3EH_U0198.png</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPWollaston Way_Wollaston Way__Basildon_SS13 1DJ_U0220.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPWollaston Way_Wollaston Way__Basildon_SS13 1DJ_U0220.png</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPCibyn Industrial Estate___Caernarfon_LL55 2BD_U0376.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPCibyn Industrial Estate___Caernarfon_LL55 2BD_U0376.png</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPApril Court_Sybron Way__Crowborough_TN6 3DZ_U0222.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPApril Court_Sybron Way__Crowborough_TN6 3DZ_U0222.png</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPA1 Business Park_Knottingley Road__Knottingley_WF11 OBU_U0366.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPA1 Business Park_Knottingley Road__Knottingley_WF11 OBU_U0366.png</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPGelli-Hirion Industrial Estate_Gelli-Hirion Industrial Estate __Pontypridd_CF37 5SX_U0375.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPGelli-Hirion Industrial Estate_Gelli-Hirion Industrial Estate __Pontypridd_CF37 5SX_U0375.png</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPD'Oriel House_Blackhill Road__Poole_BH16 6LE_U0211.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPD'Oriel House_Blackhill Road__Poole_BH16 6LE_U0211.png</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPBaglan Industrial Park_Baglan Industrial Park__Port Talbot_SA12 7BY_U0374.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBaglan Industrial Park_Baglan Industrial Park__Port Talbot_SA12 7BY_U0374.png</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPTanfield Lea North Industrial Estate_Tanfield Lea Industrial Estate North__Stanley_DH9 9XS_U0329.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPTanfield Lea North Industrial Estate_Tanfield Lea Industrial Estate North__Stanley_DH9 9XS_U0329.png</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPHyatt Trading Estate_Babbage Road__Stevenage_SG1 2TD_U0223.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPHyatt Trading Estate_Babbage Road__Stevenage_SG1 2TD_U0223.png</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPBosch Unit and Plots A-C_&amp; development sites A,B,C Gipping Way__Stowmarket _IP14 1EY_U0351.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBosch Unit and Plots A-C_&amp; development sites A,B,C Gipping Way__Stowmarket _IP14 1EY_U0351.png</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPPennywell Industrial Estate_Hylton Road__Sunderland_SR4 9EW_U0326.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPPennywell Industrial Estate_Hylton Road__Sunderland_SR4 9EW_U0326.png</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPWest Quay Court___Sunderland_SR5 2TE_U0328.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPWest Quay Court___Sunderland_SR5 2TE_U0328.png</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPSouth Marston Park_Stirling Road__Swindon_SN3 4WA_U0313.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPSouth Marston Park_Stirling Road__Swindon_SN3 4WA_U0313.png</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPThornbury Industrial Estate___Thornbury_BS35 3UP_U0228.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPThornbury Industrial Estate___Thornbury_BS35 3UP_U0228.png</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPBrambles House___Waterlooville_P07 7UW_U0231.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBrambles House___Waterlooville_P07 7UW_U0231.png</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPUnits D-F_Park Farm Industrial Estate__Wellingborough_NN8 6TY_U0153.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPUnits D-F_Park Farm Industrial Estate__Wellingborough_NN8 6TY_U0153.png</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/CTIimages/main/Images/SPEastways Industrial Estate_Eastways Industrial Estate__Witham_CM8 3YQ_U0378.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPEastways Industrial Estate_Eastways Industrial Estate__Witham_CM8 3YQ_U0378.png</t>
         </is>
       </c>
     </row>

--- a/github_image_links.xlsx
+++ b/github_image_links.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPAberaman Park Industrial Estate___Aberdare_CF44 6DA_U0377.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPAberaman Park Industrial Estate___Aberdare_CF44 6DA_U0377.png</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPHarmire Enterprise Park_Harmire Road__Barnard Castle_DL12 8BN_U0325.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPHarmire Enterprise Park_Harmire Road__Barnard Castle_DL12 8BN_U0325.png</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBakers Court_Paycocke Road__Basildon_SS14 3EH_U0198.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPBakers Court_Paycocke Road__Basildon_SS14 3EH_U0198.png</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPWollaston Way_Wollaston Way__Basildon_SS13 1DJ_U0220.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPWollaston Way_Wollaston Way__Basildon_SS13 1DJ_U0220.png</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPCibyn Industrial Estate___Caernarfon_LL55 2BD_U0376.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPCibyn Industrial Estate___Caernarfon_LL55 2BD_U0376.png</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPApril Court_Sybron Way__Crowborough_TN6 3DZ_U0222.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPApril Court_Sybron Way__Crowborough_TN6 3DZ_U0222.png</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPA1 Business Park_Knottingley Road__Knottingley_WF11 OBU_U0366.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPA1 Business Park_Knottingley Road__Knottingley_WF11 OBU_U0366.png</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPGelli-Hirion Industrial Estate_Gelli-Hirion Industrial Estate __Pontypridd_CF37 5SX_U0375.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPGelli-Hirion Industrial Estate_Gelli-Hirion Industrial Estate __Pontypridd_CF37 5SX_U0375.png</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPD'Oriel House_Blackhill Road__Poole_BH16 6LE_U0211.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPD'Oriel House_Blackhill Road__Poole_BH16 6LE_U0211.png</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBaglan Industrial Park_Baglan Industrial Park__Port Talbot_SA12 7BY_U0374.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPBaglan Industrial Park_Baglan Industrial Park__Port Talbot_SA12 7BY_U0374.png</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPTanfield Lea North Industrial Estate_Tanfield Lea Industrial Estate North__Stanley_DH9 9XS_U0329.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPTanfield Lea North Industrial Estate_Tanfield Lea Industrial Estate North__Stanley_DH9 9XS_U0329.png</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPHyatt Trading Estate_Babbage Road__Stevenage_SG1 2TD_U0223.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPHyatt Trading Estate_Babbage Road__Stevenage_SG1 2TD_U0223.png</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBosch Unit and Plots A-C_&amp; development sites A,B,C Gipping Way__Stowmarket _IP14 1EY_U0351.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPBosch Unit and Plots A-C_&amp; development sites A,B,C Gipping Way__Stowmarket _IP14 1EY_U0351.png</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPPennywell Industrial Estate_Hylton Road__Sunderland_SR4 9EW_U0326.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPPennywell Industrial Estate_Hylton Road__Sunderland_SR4 9EW_U0326.png</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPWest Quay Court___Sunderland_SR5 2TE_U0328.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPWest Quay Court___Sunderland_SR5 2TE_U0328.png</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPSouth Marston Park_Stirling Road__Swindon_SN3 4WA_U0313.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPSouth Marston Park_Stirling Road__Swindon_SN3 4WA_U0313.png</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPThornbury Industrial Estate___Thornbury_BS35 3UP_U0228.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPThornbury Industrial Estate___Thornbury_BS35 3UP_U0228.png</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPBrambles House___Waterlooville_P07 7UW_U0231.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPBrambles House___Waterlooville_P07 7UW_U0231.png</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPUnits D-F_Park Farm Industrial Estate__Wellingborough_NN8 6TY_U0153.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPUnits D-F_Park Farm Industrial Estate__Wellingborough_NN8 6TY_U0153.png</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github - CTI Final/main/Images/SPEastways Industrial Estate_Eastways Industrial Estate__Witham_CM8 3YQ_U0378.png</t>
+          <t>https://raw.githubusercontent.com/H1470/Automatic Image To Github --- CTI Final/main/Images/SPEastways Industrial Estate_Eastways Industrial Estate__Witham_CM8 3YQ_U0378.png</t>
         </is>
       </c>
     </row>
